--- a/tests/test_data/mcp_verify.xlsx
+++ b/tests/test_data/mcp_verify.xlsx
@@ -416,7 +416,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -429,7 +428,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,27 +436,13 @@
           <t>技能ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>技能名称</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>技能类型</t>
-        </is>
+      <c r="B1" t="n">
+        <v>100</v>
+      </c>
+      <c r="C1" t="n">
+        <v>200</v>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>伤害</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>冷却时间</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
         <is>
           <t>消耗法力</t>
         </is>
@@ -470,27 +454,13 @@
           <t>skill_id</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>skill_name</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>skill_type</t>
-        </is>
+      <c r="B2" t="n">
+        <v>300</v>
+      </c>
+      <c r="C2" t="n">
+        <v>400</v>
       </c>
       <c r="D2" t="inlineStr">
-        <is>
-          <t>damage</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>cooldown</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
         <is>
           <t>mp_cost</t>
         </is>
@@ -500,23 +470,13 @@
       <c r="A3" t="n">
         <v>1001</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>火球术</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>法师</t>
-        </is>
+      <c r="B3" t="n">
+        <v>500</v>
+      </c>
+      <c r="C3" t="n">
+        <v>600</v>
       </c>
       <c r="D3" t="n">
-        <v>250</v>
-      </c>
-      <c r="E3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F3" t="n">
         <v>50</v>
       </c>
     </row>
@@ -529,18 +489,10 @@
           <t>冰冻术</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>法师</t>
-        </is>
+      <c r="C4" t="n">
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>180</v>
-      </c>
-      <c r="E4" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" t="n">
         <v>60</v>
       </c>
     </row>
@@ -553,92 +505,22 @@
           <t>斩击</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>战士</t>
-        </is>
+      <c r="C5" t="n">
+        <v>2</v>
       </c>
       <c r="D5" t="n">
-        <v>300</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1004</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>暗影突袭</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>刺客</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>400</v>
-      </c>
-      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="F6" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>1005</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>治愈术</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>辅助</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>1006</v>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>雷霆一击</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>战士</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>350</v>
-      </c>
-      <c r="E8" t="n">
-        <v>4</v>
-      </c>
-      <c r="F8" t="n">
-        <v>40</v>
-      </c>
+      <c r="D6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -651,7 +533,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -824,7 +705,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -976,7 +856,6 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
